--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:03:58+00:00</t>
+    <t>2025-05-14T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1508,7 +1508,7 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-systeme-cisis</t>
   </si>
   <si>
     <t>EquipementMaterielLourd.equipementMaterielLourd</t>
@@ -2121,7 +2121,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="83.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.25" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-device-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
